--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R5" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R6" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R5" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R6" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R5" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R6" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>91656</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R5" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>91656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R6" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>91760</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R5" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>91760</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R6" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>91762</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R5" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>91762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R6" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>91763</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R5" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>91762</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R6" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128261926</v>
       </c>
       <c r="B5" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128261935</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44392-2024 artfynd.xlsx
+++ b/artfynd/A 44392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261931</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261930</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128261936</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261926</v>
+        <v>128261935</v>
       </c>
       <c r="B5" t="n">
-        <v>91790</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780861</v>
+        <v>780865</v>
       </c>
       <c r="R5" t="n">
-        <v>7368036</v>
+        <v>7368034</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261935</v>
+        <v>128261926</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>91800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780865</v>
+        <v>780861</v>
       </c>
       <c r="R6" t="n">
-        <v>7368034</v>
+        <v>7368036</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1163,7 +1163,7 @@
         <v>128261932</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128261929</v>
       </c>
       <c r="B8" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
